--- a/output/pdf_financials_xlsx/USCM.xlsx
+++ b/output/pdf_financials_xlsx/USCM.xlsx
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.882084</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.033273</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.537008</v>
       </c>
     </row>
     <row r="93">
@@ -3103,7 +3103,11 @@
           <t>Share-based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3132,7 +3136,11 @@
           <t>Warrants reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3485,7 +3493,11 @@
           <t>Share-based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.030311</v>
       </c>
@@ -3514,7 +3526,11 @@
           <t>Warrants reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>2.851773</v>
       </c>

--- a/output/pdf_financials_xlsx/USCM.xlsx
+++ b/output/pdf_financials_xlsx/USCM.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.444325</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.083979</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07130599999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.444325</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.083979</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07130599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/USCM.xlsx
+++ b/output/pdf_financials_xlsx/USCM.xlsx
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.458898</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.576499</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.807316</v>
       </c>
     </row>
     <row r="65">
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.134316</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.032941</v>
       </c>
     </row>
     <row r="68">
